--- a/xlsx/Stattkus.xlsx
+++ b/xlsx/Stattkus.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Program Files\Kingsoft\WPS Office\12.1.0.29158\office6\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Parker\WebstormProjects\konzert-public-data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -35,7 +35,19 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="847" uniqueCount="655">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="907" uniqueCount="665">
+  <si>
+    <t>SORT</t>
+  </si>
+  <si>
+    <t>Catalogue</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
   <si>
     <t>SV 1</t>
   </si>
@@ -43,7 +55,7 @@
     <t>Qual si può dir maggiore</t>
   </si>
   <si>
-    <t>Canzonette</t>
+    <t>Canzonetta</t>
   </si>
   <si>
     <t>SV 2</t>
@@ -1129,6 +1141,9 @@
     <t>Dixit dominus I, a  8</t>
   </si>
   <si>
+    <t>Psalm</t>
+  </si>
+  <si>
     <t>SV 192</t>
   </si>
   <si>
@@ -1333,6 +1348,9 @@
     <t>Salve crux pretiosa</t>
   </si>
   <si>
+    <t>Motet</t>
+  </si>
+  <si>
     <t>SV 224</t>
   </si>
   <si>
@@ -1465,6 +1483,9 @@
     <t>Balletto: De la bellezza le dovute lodi</t>
   </si>
   <si>
+    <t>Balletto</t>
+  </si>
+  <si>
     <t>SV 246</t>
   </si>
   <si>
@@ -1675,6 +1696,9 @@
     <t>Sanctorum meritis I</t>
   </si>
   <si>
+    <t>Hymn</t>
+  </si>
+  <si>
     <t>SV 278</t>
   </si>
   <si>
@@ -1717,6 +1741,9 @@
     <t>Magnificat I, a  6</t>
   </si>
   <si>
+    <t>Magnificat</t>
+  </si>
+  <si>
     <t>SV 282</t>
   </si>
   <si>
@@ -1844,6 +1871,9 @@
   </si>
   <si>
     <t>L'Incoronazione di Poppea</t>
+  </si>
+  <si>
+    <t>Opera</t>
   </si>
   <si>
     <t>SV 309</t>
@@ -2621,7 +2651,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2633,9 +2663,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -3162,7 +3189,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:D331"/>
+  <dimension ref="A1:D331"/>
   <sheetFormatPr defaultColWidth="8.61261261261261" defaultRowHeight="16.7" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="8.35135135135135" style="1" customWidth="1"/>
@@ -3172,18 +3199,32 @@
     <col min="5" max="16384" width="8.61261261261261" style="2"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>5</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -3191,13 +3232,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>8</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -3205,13 +3246,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -3219,13 +3260,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>8</v>
+        <v>11</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -3233,13 +3274,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>10</v>
+        <v>13</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -3247,13 +3288,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -3261,13 +3302,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>18</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -3275,13 +3316,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>16</v>
+        <v>19</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -3289,13 +3330,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>18</v>
+        <v>21</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -3303,13 +3344,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -3317,13 +3358,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -3331,13 +3372,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>24</v>
+        <v>27</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -3345,13 +3386,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -3359,13 +3400,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -3373,13 +3414,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>30</v>
+        <v>33</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -3387,13 +3428,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -3401,13 +3442,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -3415,13 +3456,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>36</v>
+        <v>39</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>40</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -3429,13 +3470,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -3443,13 +3484,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -3457,13 +3498,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -3471,13 +3512,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>44</v>
+        <v>47</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -3485,13 +3526,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>47</v>
+        <v>50</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>51</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -3499,13 +3540,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>53</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -3513,13 +3554,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>55</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -3527,13 +3568,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>57</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -3541,13 +3582,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>59</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -3555,13 +3596,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -3569,13 +3610,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -3583,13 +3624,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -3597,13 +3638,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>63</v>
+        <v>66</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>67</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -3611,13 +3652,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>65</v>
+        <v>68</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>69</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -3625,13 +3666,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>67</v>
+        <v>70</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>71</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -3639,13 +3680,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>69</v>
+        <v>72</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>73</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -3653,13 +3694,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>71</v>
+        <v>74</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>75</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -3667,13 +3708,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>73</v>
+        <v>76</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>77</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -3681,13 +3722,13 @@
         <v>37</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>75</v>
+        <v>78</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>79</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -3695,13 +3736,13 @@
         <v>38</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>77</v>
+        <v>80</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>81</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -3709,13 +3750,13 @@
         <v>39</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>79</v>
+        <v>82</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>83</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -3723,13 +3764,13 @@
         <v>40</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -3737,13 +3778,13 @@
         <v>41</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>83</v>
+        <v>86</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>87</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -3751,13 +3792,13 @@
         <v>42</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -3765,13 +3806,13 @@
         <v>43</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>87</v>
+        <v>90</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>91</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -3779,13 +3820,13 @@
         <v>44</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -3793,13 +3834,13 @@
         <v>45</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>95</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -3807,13 +3848,13 @@
         <v>46</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>93</v>
+        <v>96</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -3821,13 +3862,13 @@
         <v>47</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>95</v>
+        <v>98</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>99</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -3835,13 +3876,13 @@
         <v>48</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>97</v>
+        <v>100</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -3849,13 +3890,13 @@
         <v>49</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>99</v>
+        <v>102</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -3863,13 +3904,13 @@
         <v>50</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>101</v>
+        <v>104</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>105</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -3877,13 +3918,13 @@
         <v>51</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>107</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -3891,13 +3932,13 @@
         <v>52</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>105</v>
+        <v>108</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -3905,13 +3946,13 @@
         <v>53</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>107</v>
+        <v>110</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>111</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -3919,13 +3960,13 @@
         <v>54</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C55" s="4" t="s">
-        <v>109</v>
+        <v>112</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>113</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -3933,13 +3974,13 @@
         <v>55</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C56" s="4" t="s">
-        <v>111</v>
+        <v>114</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>115</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -3947,13 +3988,13 @@
         <v>56</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="C57" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>117</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -3961,13 +4002,13 @@
         <v>57</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C58" s="4" t="s">
-        <v>115</v>
+        <v>118</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -3975,13 +4016,13 @@
         <v>58</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C59" s="4" t="s">
-        <v>117</v>
+        <v>120</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>121</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -3989,13 +4030,13 @@
         <v>59</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>119</v>
+        <v>122</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>123</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -4003,13 +4044,13 @@
         <v>60</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="C61" s="4" t="s">
-        <v>121</v>
+        <v>124</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -4017,13 +4058,13 @@
         <v>61</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>123</v>
+        <v>126</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>127</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -4031,13 +4072,13 @@
         <v>62</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="C63" s="4" t="s">
-        <v>125</v>
+        <v>128</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>129</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -4045,13 +4086,13 @@
         <v>63</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C64" s="4" t="s">
-        <v>127</v>
+        <v>130</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>131</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -4059,13 +4100,13 @@
         <v>64</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="C65" s="4" t="s">
-        <v>129</v>
+        <v>132</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>133</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -4073,13 +4114,13 @@
         <v>65</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="C66" s="4" t="s">
-        <v>131</v>
+        <v>134</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>135</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -4087,13 +4128,13 @@
         <v>66</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="C67" s="4" t="s">
-        <v>133</v>
+        <v>136</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>137</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -4101,13 +4142,13 @@
         <v>67</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="C68" s="4" t="s">
-        <v>135</v>
+        <v>138</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>139</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -4115,13 +4156,13 @@
         <v>68</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="C69" s="4" t="s">
-        <v>137</v>
+        <v>140</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>141</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -4129,13 +4170,13 @@
         <v>69</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="C70" s="4" t="s">
-        <v>139</v>
+        <v>142</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>143</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -4143,13 +4184,13 @@
         <v>70</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="C71" s="4" t="s">
-        <v>141</v>
+        <v>144</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>145</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -4157,13 +4198,13 @@
         <v>71</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C72" s="4" t="s">
-        <v>143</v>
+        <v>146</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>147</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -4171,13 +4212,13 @@
         <v>72</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="C73" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>149</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -4185,13 +4226,13 @@
         <v>73</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="C74" s="4" t="s">
-        <v>147</v>
+        <v>150</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>151</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -4199,13 +4240,13 @@
         <v>74</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="C75" s="4" t="s">
-        <v>149</v>
+        <v>152</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>153</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -4213,13 +4254,13 @@
         <v>75</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C76" s="4" t="s">
-        <v>151</v>
+        <v>154</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>155</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -4227,13 +4268,13 @@
         <v>76</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="C77" s="4" t="s">
-        <v>153</v>
+        <v>156</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>157</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -4241,13 +4282,13 @@
         <v>77</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="C78" s="4" t="s">
-        <v>155</v>
+        <v>158</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>159</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -4255,13 +4296,13 @@
         <v>78</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="C79" s="4" t="s">
-        <v>157</v>
+        <v>160</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>161</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -4269,13 +4310,13 @@
         <v>79</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C80" s="4" t="s">
-        <v>159</v>
+        <v>162</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>163</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -4283,13 +4324,13 @@
         <v>80</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="C81" s="4" t="s">
-        <v>161</v>
+        <v>164</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -4297,13 +4338,13 @@
         <v>81</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="C82" s="4" t="s">
-        <v>163</v>
+        <v>166</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>167</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -4311,13 +4352,13 @@
         <v>82</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="C83" s="4" t="s">
-        <v>165</v>
+        <v>168</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>169</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -4325,13 +4366,13 @@
         <v>83</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="C84" s="4" t="s">
-        <v>167</v>
+        <v>170</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>171</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -4339,13 +4380,13 @@
         <v>84</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="C85" s="4" t="s">
-        <v>169</v>
+        <v>172</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>173</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -4353,13 +4394,13 @@
         <v>85</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="C86" s="4" t="s">
-        <v>171</v>
+        <v>174</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>175</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -4367,13 +4408,13 @@
         <v>86</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="C87" s="4" t="s">
-        <v>173</v>
+        <v>176</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>177</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -4381,13 +4422,13 @@
         <v>87</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="C88" s="4" t="s">
-        <v>175</v>
+        <v>178</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>179</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -4395,13 +4436,13 @@
         <v>88</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="C89" s="4" t="s">
-        <v>177</v>
+        <v>180</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>181</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -4409,13 +4450,13 @@
         <v>89</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C90" s="4" t="s">
-        <v>179</v>
+        <v>182</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>183</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -4423,13 +4464,13 @@
         <v>90</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="C91" s="4" t="s">
-        <v>181</v>
+        <v>184</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>185</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -4437,13 +4478,13 @@
         <v>91</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="C92" s="4" t="s">
-        <v>183</v>
+        <v>186</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>187</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -4451,13 +4492,13 @@
         <v>92</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="C93" s="4" t="s">
-        <v>185</v>
+        <v>188</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>189</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -4465,13 +4506,13 @@
         <v>93</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="C94" s="4" t="s">
-        <v>187</v>
+        <v>190</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>191</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -4479,13 +4520,13 @@
         <v>94</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="C95" s="4" t="s">
-        <v>189</v>
+        <v>192</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>193</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -4493,13 +4534,13 @@
         <v>95</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="C96" s="4" t="s">
-        <v>191</v>
+        <v>194</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>195</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -4507,13 +4548,13 @@
         <v>96</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="C97" s="4" t="s">
-        <v>193</v>
+        <v>196</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>197</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -4521,13 +4562,13 @@
         <v>97</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="C98" s="4" t="s">
-        <v>195</v>
+        <v>198</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>199</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -4535,13 +4576,13 @@
         <v>98</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="C99" s="4" t="s">
-        <v>197</v>
+        <v>200</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>201</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -4549,13 +4590,13 @@
         <v>99</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="C100" s="4" t="s">
-        <v>199</v>
+        <v>202</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>203</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -4563,13 +4604,13 @@
         <v>100</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="C101" s="4" t="s">
-        <v>201</v>
+        <v>204</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>205</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -4577,13 +4618,13 @@
         <v>101</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="C102" s="4" t="s">
-        <v>203</v>
+        <v>206</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>207</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -4591,13 +4632,13 @@
         <v>102</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="C103" s="4" t="s">
-        <v>205</v>
+        <v>208</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>209</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -4605,13 +4646,13 @@
         <v>103</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="C104" s="4" t="s">
-        <v>207</v>
+        <v>210</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>211</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -4619,13 +4660,13 @@
         <v>104</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="C105" s="4" t="s">
-        <v>209</v>
+        <v>212</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>213</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -4633,13 +4674,13 @@
         <v>105</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="C106" s="4" t="s">
-        <v>211</v>
+        <v>214</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>215</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -4647,13 +4688,13 @@
         <v>106</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C107" s="4" t="s">
-        <v>213</v>
+        <v>216</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>217</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -4661,13 +4702,13 @@
         <v>107</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="C108" s="4" t="s">
-        <v>215</v>
+        <v>218</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>219</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -4675,13 +4716,13 @@
         <v>108</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="C109" s="4" t="s">
-        <v>217</v>
+        <v>220</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>221</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -4689,13 +4730,13 @@
         <v>109</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="C110" s="4" t="s">
-        <v>219</v>
+        <v>222</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>223</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -4703,13 +4744,13 @@
         <v>110</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="C111" s="4" t="s">
-        <v>221</v>
+        <v>224</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>225</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -4717,13 +4758,13 @@
         <v>111</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="C112" s="4" t="s">
-        <v>223</v>
+        <v>226</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>227</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -4731,13 +4772,13 @@
         <v>112</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="C113" s="4" t="s">
-        <v>225</v>
+        <v>228</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>229</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -4745,13 +4786,13 @@
         <v>113</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="C114" s="4" t="s">
-        <v>227</v>
+        <v>230</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>231</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -4759,13 +4800,13 @@
         <v>114</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="C115" s="4" t="s">
-        <v>229</v>
+        <v>232</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>233</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -4773,13 +4814,13 @@
         <v>114.1</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="C116" s="4" t="s">
-        <v>229</v>
+        <v>234</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>233</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -4787,13 +4828,13 @@
         <v>115</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="C117" s="4" t="s">
-        <v>232</v>
+        <v>235</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>236</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -4801,13 +4842,13 @@
         <v>116</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="C118" s="4" t="s">
-        <v>234</v>
+        <v>237</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>238</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -4815,13 +4856,13 @@
         <v>116.1</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="C119" s="4" t="s">
-        <v>234</v>
+        <v>239</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>238</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -4829,13 +4870,13 @@
         <v>117</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="C120" s="4" t="s">
-        <v>237</v>
+        <v>240</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>241</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -4843,13 +4884,13 @@
         <v>118</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="C121" s="4" t="s">
-        <v>239</v>
+        <v>242</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>243</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -4857,13 +4898,13 @@
         <v>119</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="C122" s="4" t="s">
-        <v>241</v>
+        <v>244</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -4871,13 +4912,13 @@
         <v>120</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="C123" s="4" t="s">
-        <v>243</v>
+        <v>246</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>247</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -4885,13 +4926,13 @@
         <v>121</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="C124" s="4" t="s">
-        <v>245</v>
+        <v>248</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>249</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -4899,13 +4940,13 @@
         <v>122</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="C125" s="4" t="s">
-        <v>247</v>
+        <v>250</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>251</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -4913,13 +4954,13 @@
         <v>123</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="C126" s="4" t="s">
-        <v>249</v>
+        <v>252</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>253</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -4927,13 +4968,13 @@
         <v>124</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="C127" s="4" t="s">
-        <v>251</v>
+        <v>254</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>255</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -4941,13 +4982,13 @@
         <v>125</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="C128" s="4" t="s">
-        <v>253</v>
+        <v>256</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>257</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -4955,13 +4996,13 @@
         <v>126</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="C129" s="4" t="s">
-        <v>255</v>
+        <v>258</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>259</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -4969,13 +5010,13 @@
         <v>127</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="C130" s="4" t="s">
-        <v>257</v>
+        <v>260</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>261</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -4983,13 +5024,13 @@
         <v>128</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="C131" s="4" t="s">
-        <v>259</v>
+        <v>262</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>263</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -4997,13 +5038,13 @@
         <v>129</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="C132" s="4" t="s">
-        <v>261</v>
+        <v>264</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>265</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -5011,13 +5052,13 @@
         <v>130</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="C133" s="4" t="s">
-        <v>263</v>
+        <v>266</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>267</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -5025,13 +5066,13 @@
         <v>131</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="C134" s="4" t="s">
-        <v>265</v>
+        <v>268</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>269</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -5039,13 +5080,13 @@
         <v>132</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="C135" s="4" t="s">
-        <v>267</v>
+        <v>270</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>271</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -5053,13 +5094,13 @@
         <v>133</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="C136" s="4" t="s">
-        <v>269</v>
+        <v>272</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>273</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -5067,13 +5108,13 @@
         <v>134</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="C137" s="4" t="s">
-        <v>271</v>
+        <v>274</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>275</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -5081,13 +5122,13 @@
         <v>135</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="C138" s="4" t="s">
-        <v>273</v>
+        <v>276</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>277</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -5095,13 +5136,13 @@
         <v>136</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="C139" s="4" t="s">
-        <v>275</v>
+        <v>278</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>279</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -5109,13 +5150,13 @@
         <v>137</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="C140" s="4" t="s">
-        <v>277</v>
+        <v>280</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>281</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -5123,13 +5164,13 @@
         <v>138</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="C141" s="4" t="s">
-        <v>279</v>
+        <v>282</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>283</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -5137,13 +5178,13 @@
         <v>139</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="C142" s="4" t="s">
-        <v>281</v>
+        <v>284</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>285</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -5151,13 +5192,13 @@
         <v>140</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="C143" s="4" t="s">
-        <v>283</v>
+        <v>286</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>287</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -5165,13 +5206,13 @@
         <v>141</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="C144" s="4" t="s">
-        <v>285</v>
+        <v>288</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>289</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -5179,13 +5220,13 @@
         <v>142</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="C145" s="4" t="s">
-        <v>287</v>
+        <v>290</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>291</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -5193,13 +5234,13 @@
         <v>143</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="C146" s="4" t="s">
-        <v>289</v>
+        <v>292</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>293</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -5207,13 +5248,13 @@
         <v>144</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="C147" s="4" t="s">
-        <v>291</v>
+        <v>294</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>295</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -5221,13 +5262,13 @@
         <v>145</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="C148" s="4" t="s">
-        <v>293</v>
+        <v>296</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>297</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -5235,13 +5276,13 @@
         <v>146</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="C149" s="4" t="s">
-        <v>295</v>
+        <v>298</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>299</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -5249,13 +5290,13 @@
         <v>147</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="C150" s="4" t="s">
-        <v>297</v>
+        <v>300</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>301</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -5263,13 +5304,13 @@
         <v>148</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="C151" s="4" t="s">
-        <v>299</v>
+        <v>302</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>303</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -5277,13 +5318,13 @@
         <v>149</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="C152" s="4" t="s">
-        <v>301</v>
+        <v>304</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>305</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -5291,13 +5332,13 @@
         <v>150</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="C153" s="4" t="s">
-        <v>303</v>
+        <v>306</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>307</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -5305,13 +5346,13 @@
         <v>151</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="C154" s="4" t="s">
-        <v>305</v>
+        <v>308</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>309</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -5319,13 +5360,13 @@
         <v>152</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="C155" s="4" t="s">
-        <v>307</v>
+        <v>310</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>311</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -5333,13 +5374,13 @@
         <v>153</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="C156" s="4" t="s">
-        <v>309</v>
+        <v>312</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>313</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -5347,13 +5388,13 @@
         <v>154</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="C157" s="4" t="s">
-        <v>311</v>
+        <v>314</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>315</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -5361,13 +5402,13 @@
         <v>155</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="C158" s="4" t="s">
-        <v>313</v>
+        <v>316</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>317</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -5375,13 +5416,13 @@
         <v>156</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="C159" s="4" t="s">
-        <v>315</v>
+        <v>318</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>319</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -5389,13 +5430,13 @@
         <v>157</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="C160" s="4" t="s">
-        <v>317</v>
+        <v>320</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>321</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -5403,13 +5444,13 @@
         <v>158</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="C161" s="4" t="s">
-        <v>319</v>
+        <v>322</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>323</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -5417,13 +5458,13 @@
         <v>159</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="C162" s="4" t="s">
-        <v>321</v>
+        <v>324</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>325</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -5431,13 +5472,13 @@
         <v>160</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="C163" s="4" t="s">
-        <v>323</v>
+        <v>326</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>327</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -5445,13 +5486,13 @@
         <v>161</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="C164" s="4" t="s">
-        <v>325</v>
+        <v>328</v>
+      </c>
+      <c r="C164" s="2" t="s">
+        <v>329</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -5459,13 +5500,13 @@
         <v>162</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="C165" s="4" t="s">
-        <v>327</v>
+        <v>330</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>331</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -5473,13 +5514,13 @@
         <v>163</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="C166" s="4" t="s">
-        <v>329</v>
+        <v>332</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>333</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -5487,13 +5528,13 @@
         <v>164</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="C167" s="4" t="s">
-        <v>331</v>
+        <v>334</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>335</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -5501,13 +5542,13 @@
         <v>165</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="C168" s="4" t="s">
-        <v>333</v>
+        <v>336</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>337</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -5515,13 +5556,13 @@
         <v>166</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="C169" s="4" t="s">
-        <v>335</v>
+        <v>338</v>
+      </c>
+      <c r="C169" s="2" t="s">
+        <v>339</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -5529,13 +5570,13 @@
         <v>167</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="C170" s="4" t="s">
-        <v>337</v>
+        <v>340</v>
+      </c>
+      <c r="C170" s="2" t="s">
+        <v>341</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -5543,13 +5584,13 @@
         <v>168</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="C171" s="4" t="s">
-        <v>339</v>
+        <v>342</v>
+      </c>
+      <c r="C171" s="2" t="s">
+        <v>343</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -5557,13 +5598,13 @@
         <v>169</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="C172" s="4" t="s">
-        <v>341</v>
+        <v>344</v>
+      </c>
+      <c r="C172" s="2" t="s">
+        <v>345</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -5571,13 +5612,13 @@
         <v>170</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="C173" s="4" t="s">
-        <v>343</v>
+        <v>346</v>
+      </c>
+      <c r="C173" s="2" t="s">
+        <v>347</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -5585,13 +5626,13 @@
         <v>171</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="C174" s="4" t="s">
-        <v>345</v>
+        <v>348</v>
+      </c>
+      <c r="C174" s="2" t="s">
+        <v>349</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -5599,13 +5640,13 @@
         <v>172</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="C175" s="4" t="s">
-        <v>347</v>
+        <v>350</v>
+      </c>
+      <c r="C175" s="2" t="s">
+        <v>351</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -5613,13 +5654,13 @@
         <v>173</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="C176" s="4" t="s">
-        <v>349</v>
+        <v>352</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>353</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -5627,13 +5668,13 @@
         <v>174</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="C177" s="4" t="s">
-        <v>351</v>
+        <v>354</v>
+      </c>
+      <c r="C177" s="2" t="s">
+        <v>355</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -5641,13 +5682,13 @@
         <v>175</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="C178" s="4" t="s">
-        <v>353</v>
+        <v>356</v>
+      </c>
+      <c r="C178" s="2" t="s">
+        <v>357</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -5655,13 +5696,13 @@
         <v>176</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="C179" s="4" t="s">
-        <v>355</v>
+        <v>358</v>
+      </c>
+      <c r="C179" s="2" t="s">
+        <v>359</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -5669,13 +5710,13 @@
         <v>177</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="C180" s="4" t="s">
-        <v>335</v>
+        <v>360</v>
+      </c>
+      <c r="C180" s="2" t="s">
+        <v>339</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -5683,13 +5724,13 @@
         <v>178</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="C181" s="4" t="s">
-        <v>358</v>
+        <v>361</v>
+      </c>
+      <c r="C181" s="2" t="s">
+        <v>362</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -5697,13 +5738,13 @@
         <v>190</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="C182" s="4" t="s">
-        <v>360</v>
+        <v>363</v>
+      </c>
+      <c r="C182" s="2" t="s">
+        <v>364</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -5711,10 +5752,13 @@
         <v>191</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="C183" s="4" t="s">
-        <v>363</v>
+        <v>366</v>
+      </c>
+      <c r="C183" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="D183" s="1" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -5722,10 +5766,13 @@
         <v>192</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="C184" s="4" t="s">
-        <v>365</v>
+        <v>369</v>
+      </c>
+      <c r="C184" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="D184" s="1" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -5733,10 +5780,13 @@
         <v>193</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="C185" s="4" t="s">
-        <v>367</v>
+        <v>371</v>
+      </c>
+      <c r="C185" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D185" s="1" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -5744,10 +5794,13 @@
         <v>194</v>
       </c>
       <c r="B186" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="C186" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="D186" s="1" t="s">
         <v>368</v>
-      </c>
-      <c r="C186" s="4" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -5755,10 +5808,13 @@
         <v>195</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="C187" s="4" t="s">
-        <v>371</v>
+        <v>375</v>
+      </c>
+      <c r="C187" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="D187" s="1" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -5766,10 +5822,13 @@
         <v>196</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="C188" s="4" t="s">
-        <v>373</v>
+        <v>377</v>
+      </c>
+      <c r="C188" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="D188" s="1" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -5777,10 +5836,13 @@
         <v>197</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="C189" s="4" t="s">
-        <v>375</v>
+        <v>379</v>
+      </c>
+      <c r="C189" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="D189" s="1" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -5788,10 +5850,13 @@
         <v>197.1</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="C190" s="4" t="s">
-        <v>375</v>
+        <v>381</v>
+      </c>
+      <c r="C190" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="D190" s="1" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -5799,10 +5864,13 @@
         <v>198</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="C191" s="4" t="s">
-        <v>378</v>
+        <v>382</v>
+      </c>
+      <c r="C191" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="D191" s="1" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -5810,10 +5878,13 @@
         <v>199</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="C192" s="4" t="s">
-        <v>380</v>
+        <v>384</v>
+      </c>
+      <c r="C192" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="D192" s="1" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -5821,10 +5892,13 @@
         <v>200</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="C193" s="4" t="s">
-        <v>382</v>
+        <v>386</v>
+      </c>
+      <c r="C193" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="D193" s="1" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -5832,10 +5906,13 @@
         <v>201</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="C194" s="4" t="s">
-        <v>384</v>
+        <v>388</v>
+      </c>
+      <c r="C194" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="D194" s="1" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -5843,10 +5920,13 @@
         <v>202</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="C195" s="4" t="s">
-        <v>386</v>
+        <v>390</v>
+      </c>
+      <c r="C195" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="D195" s="1" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -5854,10 +5934,13 @@
         <v>203</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="C196" s="4" t="s">
-        <v>388</v>
+        <v>392</v>
+      </c>
+      <c r="C196" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="D196" s="1" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -5865,10 +5948,10 @@
         <v>204</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="C197" s="4" t="s">
-        <v>390</v>
+        <v>394</v>
+      </c>
+      <c r="C197" s="2" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -5876,13 +5959,13 @@
         <v>205</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>391</v>
-      </c>
-      <c r="C198" s="4" t="s">
-        <v>392</v>
+        <v>396</v>
+      </c>
+      <c r="C198" s="2" t="s">
+        <v>397</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -5890,13 +5973,13 @@
         <v>205.1</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="C199" s="4" t="s">
-        <v>392</v>
+        <v>398</v>
+      </c>
+      <c r="C199" s="2" t="s">
+        <v>397</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -5904,13 +5987,13 @@
         <v>206</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="C200" s="4" t="s">
-        <v>395</v>
+        <v>399</v>
+      </c>
+      <c r="C200" s="2" t="s">
+        <v>400</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -5918,13 +6001,13 @@
         <v>206.1</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="C201" s="4" t="s">
-        <v>395</v>
+        <v>402</v>
+      </c>
+      <c r="C201" s="2" t="s">
+        <v>400</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -5932,10 +6015,10 @@
         <v>207</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="C202" s="4" t="s">
-        <v>399</v>
+        <v>403</v>
+      </c>
+      <c r="C202" s="2" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -5943,10 +6026,10 @@
         <v>208</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="C203" s="4" t="s">
-        <v>401</v>
+        <v>405</v>
+      </c>
+      <c r="C203" s="2" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -5954,10 +6037,10 @@
         <v>209</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="C204" s="4" t="s">
-        <v>403</v>
+        <v>407</v>
+      </c>
+      <c r="C204" s="2" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -5965,10 +6048,10 @@
         <v>210</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="C205" s="4" t="s">
-        <v>405</v>
+        <v>409</v>
+      </c>
+      <c r="C205" s="2" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -5976,10 +6059,10 @@
         <v>211</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="C206" s="4" t="s">
-        <v>407</v>
+        <v>411</v>
+      </c>
+      <c r="C206" s="2" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -5987,10 +6070,10 @@
         <v>212</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="C207" s="4" t="s">
-        <v>409</v>
+        <v>413</v>
+      </c>
+      <c r="C207" s="2" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -5998,362 +6081,368 @@
         <v>213</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="C208" s="4" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="209" spans="1:3">
+        <v>415</v>
+      </c>
+      <c r="C208" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4">
       <c r="A209" s="3">
         <v>214</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="C209" s="4" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="210" spans="1:3">
+        <v>417</v>
+      </c>
+      <c r="C209" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4">
       <c r="A210" s="3">
         <v>215</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="C210" s="4" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="211" spans="1:3">
+        <v>419</v>
+      </c>
+      <c r="C210" s="2" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4">
       <c r="A211" s="3">
         <v>216</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="C211" s="4" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="212" spans="1:3">
+        <v>421</v>
+      </c>
+      <c r="C211" s="2" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4">
       <c r="A212" s="3">
         <v>217</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="C212" s="4" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="213" spans="1:3">
+        <v>423</v>
+      </c>
+      <c r="C212" s="2" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4">
       <c r="A213" s="3">
         <v>218</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="C213" s="4" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="214" spans="1:3">
+        <v>425</v>
+      </c>
+      <c r="C213" s="2" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4">
       <c r="A214" s="3">
         <v>219</v>
       </c>
       <c r="B214" s="3" t="s">
-        <v>422</v>
-      </c>
-      <c r="C214" s="4" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="215" spans="1:3">
+        <v>427</v>
+      </c>
+      <c r="C214" s="2" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4">
       <c r="A215" s="3">
         <v>220</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>424</v>
-      </c>
-      <c r="C215" s="4" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="216" spans="1:3">
+        <v>429</v>
+      </c>
+      <c r="C215" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4">
       <c r="A216" s="3">
         <v>221</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>426</v>
-      </c>
-      <c r="C216" s="4" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="217" spans="1:3">
+        <v>431</v>
+      </c>
+      <c r="C216" s="2" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4">
       <c r="A217" s="3">
         <v>222</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>428</v>
-      </c>
-      <c r="C217" s="4" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="218" spans="1:3">
+        <v>433</v>
+      </c>
+      <c r="C217" s="2" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4">
       <c r="A218" s="3">
         <v>223</v>
       </c>
       <c r="B218" s="3" t="s">
-        <v>430</v>
-      </c>
-      <c r="C218" s="4" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="219" spans="1:3">
+        <v>435</v>
+      </c>
+      <c r="C218" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="D218" s="1" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4">
       <c r="A219" s="3">
         <v>224</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>432</v>
-      </c>
-      <c r="C219" s="4" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="220" spans="1:3">
+        <v>438</v>
+      </c>
+      <c r="C219" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4">
       <c r="A220" s="3">
         <v>225</v>
       </c>
       <c r="B220" s="3" t="s">
-        <v>434</v>
-      </c>
-      <c r="C220" s="4" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="221" spans="1:3">
+        <v>440</v>
+      </c>
+      <c r="C220" s="2" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4">
       <c r="A221" s="3">
         <v>226</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>436</v>
-      </c>
-      <c r="C221" s="4" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="222" spans="1:3">
+        <v>442</v>
+      </c>
+      <c r="C221" s="2" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4">
       <c r="A222" s="3">
         <v>227</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>438</v>
-      </c>
-      <c r="C222" s="4" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="223" spans="1:3">
+        <v>444</v>
+      </c>
+      <c r="C222" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4">
       <c r="A223" s="3">
         <v>228</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>440</v>
-      </c>
-      <c r="C223" s="4" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="224" spans="1:3">
+        <v>446</v>
+      </c>
+      <c r="C223" s="2" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4">
       <c r="A224" s="3">
         <v>229</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="C224" s="4" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="225" spans="1:3">
+        <v>448</v>
+      </c>
+      <c r="C224" s="2" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4">
       <c r="A225" s="3">
         <v>230</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>444</v>
-      </c>
-      <c r="C225" s="4" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="226" spans="1:3">
+        <v>450</v>
+      </c>
+      <c r="C225" s="2" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4">
       <c r="A226" s="3">
         <v>231</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>446</v>
-      </c>
-      <c r="C226" s="4" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="227" spans="1:3">
+        <v>452</v>
+      </c>
+      <c r="C226" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4">
       <c r="A227" s="3">
         <v>232</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="C227" s="4" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="228" spans="1:3">
+        <v>454</v>
+      </c>
+      <c r="C227" s="2" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4">
       <c r="A228" s="3">
         <v>233</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="C228" s="4" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="229" spans="1:3">
+        <v>456</v>
+      </c>
+      <c r="C228" s="2" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4">
       <c r="A229" s="3">
         <v>234</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>452</v>
-      </c>
-      <c r="C229" s="4" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="230" spans="1:3">
+        <v>458</v>
+      </c>
+      <c r="C229" s="2" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4">
       <c r="A230" s="3">
         <v>235</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>454</v>
-      </c>
-      <c r="C230" s="4" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="231" spans="1:3">
+        <v>460</v>
+      </c>
+      <c r="C230" s="2" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4">
       <c r="A231" s="3">
         <v>236</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>456</v>
-      </c>
-      <c r="C231" s="4" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="232" spans="1:3">
+        <v>462</v>
+      </c>
+      <c r="C231" s="2" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4">
       <c r="A232" s="3">
         <v>237</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>458</v>
-      </c>
-      <c r="C232" s="4" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="233" spans="1:3">
+        <v>464</v>
+      </c>
+      <c r="C232" s="2" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4">
       <c r="A233" s="3">
         <v>238</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>460</v>
-      </c>
-      <c r="C233" s="4" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="234" spans="1:3">
+        <v>466</v>
+      </c>
+      <c r="C233" s="2" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4">
       <c r="A234" s="3">
         <v>239</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>462</v>
-      </c>
-      <c r="C234" s="4" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="235" spans="1:3">
+        <v>468</v>
+      </c>
+      <c r="C234" s="2" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4">
       <c r="A235" s="3">
         <v>240</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>464</v>
-      </c>
-      <c r="C235" s="4" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="236" spans="1:3">
+        <v>470</v>
+      </c>
+      <c r="C235" s="2" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4">
       <c r="A236" s="3">
         <v>241</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>466</v>
-      </c>
-      <c r="C236" s="4" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="237" spans="1:3">
+        <v>472</v>
+      </c>
+      <c r="C236" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4">
       <c r="A237" s="3">
         <v>242</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="C237" s="4" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="238" spans="1:3">
+        <v>474</v>
+      </c>
+      <c r="C237" s="2" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4">
       <c r="A238" s="3">
         <v>243</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>470</v>
-      </c>
-      <c r="C238" s="4" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="239" spans="1:3">
+        <v>476</v>
+      </c>
+      <c r="C238" s="2" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4">
       <c r="A239" s="3">
         <v>244</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>472</v>
-      </c>
-      <c r="C239" s="4" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="240" spans="1:3">
+        <v>478</v>
+      </c>
+      <c r="C239" s="2" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4">
       <c r="A240" s="3">
         <v>245</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>474</v>
-      </c>
-      <c r="C240" s="4" t="s">
-        <v>475</v>
+        <v>480</v>
+      </c>
+      <c r="C240" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="D240" s="1" t="s">
+        <v>482</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -6361,10 +6450,10 @@
         <v>246</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>476</v>
-      </c>
-      <c r="C241" s="4" t="s">
-        <v>477</v>
+        <v>483</v>
+      </c>
+      <c r="C241" s="2" t="s">
+        <v>484</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -6372,10 +6461,10 @@
         <v>247</v>
       </c>
       <c r="B242" s="3" t="s">
-        <v>478</v>
-      </c>
-      <c r="C242" s="4" t="s">
-        <v>479</v>
+        <v>485</v>
+      </c>
+      <c r="C242" s="2" t="s">
+        <v>486</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -6383,10 +6472,10 @@
         <v>248</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>480</v>
-      </c>
-      <c r="C243" s="4" t="s">
-        <v>481</v>
+        <v>487</v>
+      </c>
+      <c r="C243" s="2" t="s">
+        <v>488</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -6394,10 +6483,13 @@
         <v>249</v>
       </c>
       <c r="B244" s="3" t="s">
-        <v>482</v>
-      </c>
-      <c r="C244" s="4" t="s">
-        <v>483</v>
+        <v>489</v>
+      </c>
+      <c r="C244" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="D244" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -6405,10 +6497,13 @@
         <v>249.1</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>484</v>
-      </c>
-      <c r="C245" s="4" t="s">
-        <v>483</v>
+        <v>491</v>
+      </c>
+      <c r="C245" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="D245" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -6416,10 +6511,10 @@
         <v>250</v>
       </c>
       <c r="B246" s="3" t="s">
-        <v>485</v>
-      </c>
-      <c r="C246" s="4" t="s">
-        <v>486</v>
+        <v>492</v>
+      </c>
+      <c r="C246" s="2" t="s">
+        <v>493</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -6427,10 +6522,10 @@
         <v>251</v>
       </c>
       <c r="B247" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="C247" s="4" t="s">
-        <v>488</v>
+        <v>494</v>
+      </c>
+      <c r="C247" s="2" t="s">
+        <v>495</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -6438,10 +6533,10 @@
         <v>252</v>
       </c>
       <c r="B248" s="3" t="s">
-        <v>489</v>
-      </c>
-      <c r="C248" s="4" t="s">
-        <v>490</v>
+        <v>496</v>
+      </c>
+      <c r="C248" s="2" t="s">
+        <v>497</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -6449,10 +6544,10 @@
         <v>253</v>
       </c>
       <c r="B249" s="3" t="s">
-        <v>491</v>
-      </c>
-      <c r="C249" s="4" t="s">
-        <v>492</v>
+        <v>498</v>
+      </c>
+      <c r="C249" s="2" t="s">
+        <v>499</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -6460,10 +6555,10 @@
         <v>254</v>
       </c>
       <c r="B250" s="3" t="s">
-        <v>493</v>
-      </c>
-      <c r="C250" s="4" t="s">
-        <v>494</v>
+        <v>500</v>
+      </c>
+      <c r="C250" s="2" t="s">
+        <v>501</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -6471,10 +6566,10 @@
         <v>255</v>
       </c>
       <c r="B251" s="3" t="s">
-        <v>495</v>
-      </c>
-      <c r="C251" s="4" t="s">
-        <v>496</v>
+        <v>502</v>
+      </c>
+      <c r="C251" s="2" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -6482,10 +6577,10 @@
         <v>256</v>
       </c>
       <c r="B252" s="3" t="s">
-        <v>497</v>
-      </c>
-      <c r="C252" s="4" t="s">
-        <v>498</v>
+        <v>504</v>
+      </c>
+      <c r="C252" s="2" t="s">
+        <v>505</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -6493,13 +6588,13 @@
         <v>257</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>499</v>
-      </c>
-      <c r="C253" s="4" t="s">
-        <v>500</v>
+        <v>506</v>
+      </c>
+      <c r="C253" s="2" t="s">
+        <v>507</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -6507,13 +6602,13 @@
         <v>257.1</v>
       </c>
       <c r="B254" s="3" t="s">
-        <v>501</v>
-      </c>
-      <c r="C254" s="4" t="s">
-        <v>500</v>
+        <v>508</v>
+      </c>
+      <c r="C254" s="2" t="s">
+        <v>507</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -6521,10 +6616,10 @@
         <v>258</v>
       </c>
       <c r="B255" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="C255" s="4" t="s">
-        <v>503</v>
+        <v>509</v>
+      </c>
+      <c r="C255" s="2" t="s">
+        <v>510</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -6532,835 +6627,949 @@
         <v>259</v>
       </c>
       <c r="B256" s="3" t="s">
-        <v>504</v>
-      </c>
-      <c r="C256" s="4" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="257" spans="1:3">
+        <v>511</v>
+      </c>
+      <c r="C256" s="2" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4">
       <c r="A257" s="3">
         <v>260</v>
       </c>
       <c r="B257" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="C257" s="4" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="258" spans="1:3">
+        <v>513</v>
+      </c>
+      <c r="C257" s="2" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4">
       <c r="A258" s="3">
         <v>261</v>
       </c>
       <c r="B258" s="3" t="s">
-        <v>508</v>
-      </c>
-      <c r="C258" s="4" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="259" spans="1:3">
+        <v>515</v>
+      </c>
+      <c r="C258" s="2" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4">
       <c r="A259" s="3">
         <v>262</v>
       </c>
       <c r="B259" s="3" t="s">
-        <v>510</v>
-      </c>
-      <c r="C259" s="4" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="260" spans="1:3">
+        <v>517</v>
+      </c>
+      <c r="C259" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="D259" s="1" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4">
       <c r="A260" s="3">
         <v>263</v>
       </c>
       <c r="B260" s="3" t="s">
-        <v>512</v>
-      </c>
-      <c r="C260" s="4" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="261" spans="1:3">
+        <v>519</v>
+      </c>
+      <c r="C260" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="D260" s="1" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4">
       <c r="A261" s="3">
         <v>264</v>
       </c>
       <c r="B261" s="3" t="s">
-        <v>514</v>
-      </c>
-      <c r="C261" s="4" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="262" spans="1:3">
+        <v>521</v>
+      </c>
+      <c r="C261" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="D261" s="1" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4">
       <c r="A262" s="3">
         <v>265</v>
       </c>
       <c r="B262" s="3" t="s">
-        <v>516</v>
-      </c>
-      <c r="C262" s="4" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="263" spans="1:3">
+        <v>523</v>
+      </c>
+      <c r="C262" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="D262" s="1" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4">
       <c r="A263" s="3">
         <v>266</v>
       </c>
       <c r="B263" s="3" t="s">
-        <v>518</v>
-      </c>
-      <c r="C263" s="4" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="264" spans="1:3">
+        <v>525</v>
+      </c>
+      <c r="C263" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="D263" s="1" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4">
       <c r="A264" s="3">
         <v>267</v>
       </c>
       <c r="B264" s="3" t="s">
-        <v>520</v>
-      </c>
-      <c r="C264" s="4" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="265" spans="1:3">
+        <v>527</v>
+      </c>
+      <c r="C264" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="D264" s="1" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4">
       <c r="A265" s="1">
         <v>267.1</v>
       </c>
       <c r="B265" s="3" t="s">
-        <v>522</v>
-      </c>
-      <c r="C265" s="4" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="266" spans="1:3">
+        <v>529</v>
+      </c>
+      <c r="C265" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="D265" s="1" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4">
       <c r="A266" s="3">
         <v>268</v>
       </c>
       <c r="B266" s="3" t="s">
-        <v>524</v>
-      </c>
-      <c r="C266" s="4" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="267" spans="1:3">
+        <v>531</v>
+      </c>
+      <c r="C266" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="D266" s="1" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4">
       <c r="A267" s="3">
         <v>269</v>
       </c>
       <c r="B267" s="3" t="s">
-        <v>526</v>
-      </c>
-      <c r="C267" s="4" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="268" spans="1:3">
+        <v>533</v>
+      </c>
+      <c r="C267" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="D267" s="1" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4">
       <c r="A268" s="3">
         <v>270</v>
       </c>
       <c r="B268" s="3" t="s">
-        <v>528</v>
-      </c>
-      <c r="C268" s="4" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="269" spans="1:3">
+        <v>535</v>
+      </c>
+      <c r="C268" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="D268" s="1" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4">
       <c r="A269" s="3">
         <v>271</v>
       </c>
       <c r="B269" s="3" t="s">
-        <v>530</v>
-      </c>
-      <c r="C269" s="4" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="270" spans="1:3">
+        <v>537</v>
+      </c>
+      <c r="C269" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="D269" s="1" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4">
       <c r="A270" s="3">
         <v>272</v>
       </c>
       <c r="B270" s="3" t="s">
-        <v>532</v>
-      </c>
-      <c r="C270" s="4" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="271" spans="1:3">
+        <v>539</v>
+      </c>
+      <c r="C270" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="D270" s="1" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4">
       <c r="A271" s="1">
         <v>272.1</v>
       </c>
       <c r="B271" s="3" t="s">
-        <v>534</v>
-      </c>
-      <c r="C271" s="4" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="272" spans="1:3">
+        <v>541</v>
+      </c>
+      <c r="C271" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="D271" s="1" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4">
       <c r="A272" s="3">
         <v>273</v>
       </c>
       <c r="B272" s="3" t="s">
-        <v>536</v>
-      </c>
-      <c r="C272" s="4" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="273" spans="1:3">
+        <v>543</v>
+      </c>
+      <c r="C272" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="D272" s="1" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4">
       <c r="A273" s="3">
         <v>274</v>
       </c>
       <c r="B273" s="3" t="s">
-        <v>538</v>
-      </c>
-      <c r="C273" s="4" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="274" spans="1:3">
+        <v>545</v>
+      </c>
+      <c r="C273" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="D273" s="1" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4">
       <c r="A274" s="3">
         <v>275</v>
       </c>
       <c r="B274" s="3" t="s">
-        <v>540</v>
-      </c>
-      <c r="C274" s="4" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="275" spans="1:3">
+        <v>547</v>
+      </c>
+      <c r="C274" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4">
       <c r="A275" s="3">
         <v>276</v>
       </c>
       <c r="B275" s="3" t="s">
-        <v>542</v>
-      </c>
-      <c r="C275" s="4" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="276" spans="1:3">
+        <v>549</v>
+      </c>
+      <c r="C275" s="2" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4">
       <c r="A276" s="3">
         <v>277</v>
       </c>
       <c r="B276" s="3" t="s">
-        <v>544</v>
-      </c>
-      <c r="C276" s="4" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="277" spans="1:3">
+        <v>551</v>
+      </c>
+      <c r="C276" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="D276" s="1" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4">
       <c r="A277" s="3">
         <v>278</v>
       </c>
       <c r="B277" s="3" t="s">
-        <v>546</v>
-      </c>
-      <c r="C277" s="4" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="278" spans="1:3">
+        <v>554</v>
+      </c>
+      <c r="C277" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="D277" s="1" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4">
       <c r="A278" s="1">
         <v>278.1</v>
       </c>
       <c r="B278" s="3" t="s">
-        <v>548</v>
-      </c>
-      <c r="C278" s="4" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="279" spans="1:3">
+        <v>556</v>
+      </c>
+      <c r="C278" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="D278" s="1" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4">
       <c r="A279" s="1">
         <v>278.2</v>
       </c>
       <c r="B279" s="3" t="s">
-        <v>550</v>
-      </c>
-      <c r="C279" s="4" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="280" spans="1:3">
+        <v>558</v>
+      </c>
+      <c r="C279" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="D279" s="1" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4">
       <c r="A280" s="3">
         <v>279</v>
       </c>
       <c r="B280" s="3" t="s">
-        <v>552</v>
-      </c>
-      <c r="C280" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="C280" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="D280" s="1" t="s">
         <v>553</v>
       </c>
     </row>
-    <row r="281" spans="1:3">
+    <row r="281" spans="1:4">
       <c r="A281" s="1">
         <v>279.1</v>
       </c>
       <c r="B281" s="3" t="s">
-        <v>554</v>
-      </c>
-      <c r="C281" s="4" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="282" spans="1:3">
+        <v>562</v>
+      </c>
+      <c r="C281" s="2" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4">
       <c r="A282" s="3">
         <v>280</v>
       </c>
       <c r="B282" s="3" t="s">
-        <v>556</v>
-      </c>
-      <c r="C282" s="4" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="283" spans="1:3">
+        <v>564</v>
+      </c>
+      <c r="C282" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="D282" s="1" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4">
       <c r="A283" s="3">
         <v>281</v>
       </c>
       <c r="B283" s="3" t="s">
-        <v>558</v>
-      </c>
-      <c r="C283" s="4" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="284" spans="1:3">
+        <v>566</v>
+      </c>
+      <c r="C283" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="D283" s="1" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4">
       <c r="A284" s="3">
         <v>282</v>
       </c>
       <c r="B284" s="3" t="s">
-        <v>560</v>
-      </c>
-      <c r="C284" s="4" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="285" spans="1:3">
+        <v>569</v>
+      </c>
+      <c r="C284" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="D284" s="1" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4">
       <c r="A285" s="3">
         <v>283</v>
       </c>
       <c r="B285" s="3" t="s">
-        <v>562</v>
-      </c>
-      <c r="C285" s="4" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="286" spans="1:3">
+        <v>571</v>
+      </c>
+      <c r="C285" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="D285" s="1" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4">
       <c r="A286" s="3">
         <v>284</v>
       </c>
       <c r="B286" s="3" t="s">
-        <v>564</v>
-      </c>
-      <c r="C286" s="4" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="287" spans="1:3">
+        <v>573</v>
+      </c>
+      <c r="C286" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="D286" s="1" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4">
       <c r="A287" s="3">
         <v>285</v>
       </c>
       <c r="B287" s="3" t="s">
-        <v>566</v>
-      </c>
-      <c r="C287" s="4" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="288" spans="1:3">
+        <v>575</v>
+      </c>
+      <c r="C287" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="D287" s="1" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4">
       <c r="A288" s="3">
         <v>286</v>
       </c>
       <c r="B288" s="3" t="s">
-        <v>568</v>
-      </c>
-      <c r="C288" s="4" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="289" spans="1:3">
+        <v>577</v>
+      </c>
+      <c r="C288" s="2" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4">
       <c r="A289" s="3">
         <v>287</v>
       </c>
       <c r="B289" s="3" t="s">
-        <v>570</v>
-      </c>
-      <c r="C289" s="4" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="290" spans="1:3">
+        <v>579</v>
+      </c>
+      <c r="C289" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="D289" s="1" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4">
       <c r="A290" s="3">
         <v>288</v>
       </c>
       <c r="B290" s="3" t="s">
-        <v>572</v>
-      </c>
-      <c r="C290" s="4" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="291" spans="1:3">
+        <v>581</v>
+      </c>
+      <c r="C290" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4">
       <c r="A291" s="3">
         <v>294</v>
       </c>
       <c r="B291" s="3" t="s">
-        <v>574</v>
-      </c>
-      <c r="C291" s="4" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="292" spans="1:3">
+        <v>583</v>
+      </c>
+      <c r="C291" s="2" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4">
       <c r="A292" s="3">
         <v>295</v>
       </c>
       <c r="B292" s="3" t="s">
-        <v>576</v>
-      </c>
-      <c r="C292" s="4" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="293" spans="1:3">
+        <v>585</v>
+      </c>
+      <c r="C292" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="D292" s="1" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4">
       <c r="A293" s="3">
         <v>296</v>
       </c>
       <c r="B293" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="C293" s="4" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="294" spans="1:3">
+        <v>587</v>
+      </c>
+      <c r="C293" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="D293" s="1" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4">
       <c r="A294" s="3">
         <v>297</v>
       </c>
       <c r="B294" s="3" t="s">
-        <v>580</v>
-      </c>
-      <c r="C294" s="4" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="295" spans="1:3">
+        <v>589</v>
+      </c>
+      <c r="C294" s="2" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4">
       <c r="A295" s="3">
         <v>298</v>
       </c>
       <c r="B295" s="3" t="s">
-        <v>582</v>
-      </c>
-      <c r="C295" s="4" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="296" spans="1:3">
+        <v>591</v>
+      </c>
+      <c r="C295" s="2" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4">
       <c r="A296" s="3">
         <v>299</v>
       </c>
       <c r="B296" s="3" t="s">
-        <v>584</v>
-      </c>
-      <c r="C296" s="4" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="297" spans="1:3">
+        <v>593</v>
+      </c>
+      <c r="C296" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="D296" s="1" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4">
       <c r="A297" s="1">
         <v>299.1</v>
       </c>
       <c r="B297" s="3" t="s">
-        <v>586</v>
-      </c>
-      <c r="C297" s="4" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="298" spans="1:3">
+        <v>595</v>
+      </c>
+      <c r="C297" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="D297" s="1" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4">
       <c r="A298" s="3">
         <v>300</v>
       </c>
       <c r="B298" s="3" t="s">
-        <v>587</v>
-      </c>
-      <c r="C298" s="4" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="299" spans="1:3">
+        <v>596</v>
+      </c>
+      <c r="C298" s="2" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4">
       <c r="A299" s="3">
         <v>301</v>
       </c>
       <c r="B299" s="3" t="s">
-        <v>589</v>
-      </c>
-      <c r="C299" s="4" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="300" spans="1:3">
+        <v>598</v>
+      </c>
+      <c r="C299" s="2" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4">
       <c r="A300" s="3">
         <v>302</v>
       </c>
       <c r="B300" s="3" t="s">
-        <v>591</v>
-      </c>
-      <c r="C300" s="4" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="301" spans="1:3">
+        <v>600</v>
+      </c>
+      <c r="C300" s="2" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4">
       <c r="A301" s="3">
         <v>303</v>
       </c>
       <c r="B301" s="3" t="s">
-        <v>593</v>
-      </c>
-      <c r="C301" s="4" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="302" spans="1:3">
+        <v>602</v>
+      </c>
+      <c r="C301" s="2" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4">
       <c r="A302" s="3">
         <v>304</v>
       </c>
       <c r="B302" s="3" t="s">
-        <v>595</v>
-      </c>
-      <c r="C302" s="4" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="303" spans="1:3">
+        <v>604</v>
+      </c>
+      <c r="C302" s="2" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4">
       <c r="A303" s="3">
         <v>305</v>
       </c>
       <c r="B303" s="3" t="s">
-        <v>597</v>
-      </c>
-      <c r="C303" s="4" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="304" spans="1:3">
+        <v>606</v>
+      </c>
+      <c r="C303" s="2" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4">
       <c r="A304" s="3">
         <v>307</v>
       </c>
       <c r="B304" s="3" t="s">
-        <v>599</v>
-      </c>
-      <c r="C304" s="4" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="305" spans="1:3">
+        <v>608</v>
+      </c>
+      <c r="C304" s="2" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4">
       <c r="A305" s="3">
         <v>308</v>
       </c>
       <c r="B305" s="3" t="s">
-        <v>601</v>
-      </c>
-      <c r="C305" s="4" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="306" spans="1:3">
+        <v>610</v>
+      </c>
+      <c r="C305" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="D305" s="1" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4">
       <c r="A306" s="3">
         <v>309</v>
       </c>
       <c r="B306" s="3" t="s">
-        <v>603</v>
-      </c>
-      <c r="C306" s="4" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="307" spans="1:3">
+        <v>613</v>
+      </c>
+      <c r="C306" s="2" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4">
       <c r="A307" s="3">
         <v>310</v>
       </c>
       <c r="B307" s="3" t="s">
-        <v>605</v>
-      </c>
-      <c r="C307" s="4" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="308" spans="1:3">
+        <v>615</v>
+      </c>
+      <c r="C307" s="2" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4">
       <c r="A308" s="3">
         <v>311</v>
       </c>
       <c r="B308" s="3" t="s">
-        <v>607</v>
-      </c>
-      <c r="C308" s="4" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="309" spans="1:3">
+        <v>617</v>
+      </c>
+      <c r="C308" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="D308" s="1" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4">
       <c r="A309" s="3">
         <v>312</v>
       </c>
       <c r="B309" s="3" t="s">
-        <v>609</v>
-      </c>
-      <c r="C309" s="4" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="310" spans="1:3">
+        <v>619</v>
+      </c>
+      <c r="C309" s="2" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4">
       <c r="A310" s="3">
         <v>313</v>
       </c>
       <c r="B310" s="3" t="s">
-        <v>611</v>
-      </c>
-      <c r="C310" s="4" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="311" spans="1:3">
+        <v>621</v>
+      </c>
+      <c r="C310" s="2" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4">
       <c r="A311" s="3">
         <v>314</v>
       </c>
       <c r="B311" s="3" t="s">
-        <v>613</v>
-      </c>
-      <c r="C311" s="4" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="312" spans="1:3">
+        <v>623</v>
+      </c>
+      <c r="C311" s="2" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4">
       <c r="A312" s="3">
         <v>315</v>
       </c>
       <c r="B312" s="3" t="s">
-        <v>615</v>
-      </c>
-      <c r="C312" s="4" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="313" spans="1:3">
+        <v>625</v>
+      </c>
+      <c r="C312" s="2" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4">
       <c r="A313" s="3">
         <v>316</v>
       </c>
       <c r="B313" s="3" t="s">
-        <v>617</v>
-      </c>
-      <c r="C313" s="4" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="314" spans="1:3">
+        <v>627</v>
+      </c>
+      <c r="C313" s="2" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4">
       <c r="A314" s="3">
         <v>317</v>
       </c>
       <c r="B314" s="3" t="s">
-        <v>619</v>
-      </c>
-      <c r="C314" s="4" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="315" spans="1:3">
+        <v>629</v>
+      </c>
+      <c r="C314" s="2" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4">
       <c r="A315" s="3">
         <v>318</v>
       </c>
       <c r="B315" s="3" t="s">
-        <v>621</v>
-      </c>
-      <c r="C315" s="4" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="316" spans="1:3">
+        <v>631</v>
+      </c>
+      <c r="C315" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="D315" s="1" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4">
       <c r="A316" s="3">
         <v>320</v>
       </c>
       <c r="B316" s="3" t="s">
-        <v>623</v>
-      </c>
-      <c r="C316" s="4" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="317" spans="1:3">
+        <v>633</v>
+      </c>
+      <c r="C316" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4">
       <c r="A317" s="3">
         <v>321</v>
       </c>
       <c r="B317" s="3" t="s">
-        <v>625</v>
-      </c>
-      <c r="C317" s="4" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="318" spans="1:3">
+        <v>635</v>
+      </c>
+      <c r="C317" s="2" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4">
       <c r="A318" s="3">
         <v>322</v>
       </c>
       <c r="B318" s="3" t="s">
-        <v>627</v>
-      </c>
-      <c r="C318" s="4" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="319" spans="1:3">
+        <v>637</v>
+      </c>
+      <c r="C318" s="2" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4">
       <c r="A319" s="3">
         <v>324</v>
       </c>
       <c r="B319" s="3" t="s">
-        <v>629</v>
-      </c>
-      <c r="C319" s="4" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="320" spans="1:3">
+        <v>639</v>
+      </c>
+      <c r="C319" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4">
       <c r="A320" s="3">
         <v>325</v>
       </c>
       <c r="B320" s="3" t="s">
-        <v>631</v>
-      </c>
-      <c r="C320" s="4" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="321" spans="1:3">
+        <v>641</v>
+      </c>
+      <c r="C320" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="D320" s="1" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4">
       <c r="A321" s="1">
         <v>326</v>
       </c>
       <c r="B321" s="3" t="s">
-        <v>633</v>
-      </c>
-      <c r="C321" s="4" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="322" spans="1:3">
+        <v>643</v>
+      </c>
+      <c r="C321" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="D321" s="1" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4">
       <c r="A322" s="1">
         <v>327</v>
       </c>
       <c r="B322" s="3" t="s">
-        <v>635</v>
-      </c>
-      <c r="C322" s="4" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="323" spans="1:3">
+        <v>645</v>
+      </c>
+      <c r="C322" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="D322" s="1" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4">
       <c r="A323" s="1">
         <v>328</v>
       </c>
       <c r="B323" s="3" t="s">
-        <v>637</v>
-      </c>
-      <c r="C323" s="4" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="324" spans="1:3">
+        <v>647</v>
+      </c>
+      <c r="C323" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="D323" s="1" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4">
       <c r="A324" s="1">
         <v>331</v>
       </c>
       <c r="B324" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="C324" s="4" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="325" spans="1:3">
+        <v>649</v>
+      </c>
+      <c r="C324" s="2" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4">
       <c r="A325" s="3">
         <v>332</v>
       </c>
       <c r="B325" s="3" t="s">
-        <v>641</v>
-      </c>
-      <c r="C325" s="4" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="326" spans="1:3">
+        <v>651</v>
+      </c>
+      <c r="C325" s="2" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4">
       <c r="A326" s="3">
         <v>333</v>
       </c>
       <c r="B326" s="3" t="s">
-        <v>643</v>
-      </c>
-      <c r="C326" s="4" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="327" spans="1:3">
+        <v>653</v>
+      </c>
+      <c r="C326" s="2" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4">
       <c r="A327" s="3">
         <v>334</v>
       </c>
       <c r="B327" s="3" t="s">
-        <v>645</v>
-      </c>
-      <c r="C327" s="4" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="328" spans="1:3">
+        <v>655</v>
+      </c>
+      <c r="C327" s="2" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4">
       <c r="A328" s="3">
         <v>335</v>
       </c>
       <c r="B328" s="3" t="s">
-        <v>647</v>
-      </c>
-      <c r="C328" s="4" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="329" spans="1:3">
+        <v>657</v>
+      </c>
+      <c r="C328" s="2" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4">
       <c r="A329" s="3">
         <v>336</v>
       </c>
       <c r="B329" s="3" t="s">
-        <v>649</v>
-      </c>
-      <c r="C329" s="4" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="330" spans="1:3">
+        <v>659</v>
+      </c>
+      <c r="C329" s="2" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4">
       <c r="A330" s="3">
         <v>337</v>
       </c>
       <c r="B330" s="3" t="s">
-        <v>651</v>
-      </c>
-      <c r="C330" s="4" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="331" spans="1:3">
+        <v>661</v>
+      </c>
+      <c r="C330" s="2" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4">
       <c r="A331" s="1">
-        <v>999.1</v>
+        <v>999.2</v>
       </c>
       <c r="B331" s="3" t="s">
-        <v>653</v>
-      </c>
-      <c r="C331" s="4" t="s">
-        <v>654</v>
+        <v>663</v>
+      </c>
+      <c r="C331" s="2" t="s">
+        <v>664</v>
       </c>
     </row>
   </sheetData>
